--- a/diseases/d113/2026-2029.xlsx
+++ b/diseases/d113/2026-2029.xlsx
@@ -25578,12 +25578,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -25617,81 +25617,100 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R157" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0</v>
       </c>
       <c r="S157" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO157" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP157" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ157" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR157" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS157" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS157" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
+        </is>
+      </c>
       <c r="AT157" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU157" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV157" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA157" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB157" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC157" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -25718,17 +25737,17 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -25753,7 +25772,7 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
@@ -25767,76 +25786,170 @@
       <c r="O158" t="n">
         <v>0</v>
       </c>
-      <c r="R158" t="n">
-        <v>0</v>
-      </c>
-      <c r="S158" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
+        </is>
+      </c>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
+        </is>
+      </c>
+      <c r="W158" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X158" t="inlineStr">
+        <is>
+          <t>Q-feber</t>
+        </is>
+      </c>
+      <c r="Y158" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB158" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD158" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE158" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF158" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG158" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH158" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI158" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ158" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK158" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM158" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN158" t="b">
+        <v>1</v>
       </c>
       <c r="AO158" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP158" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ158" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR158" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS158" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS158" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
+        </is>
+      </c>
       <c r="AT158" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU158" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV158" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA158" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB158" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC158" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -25868,12 +25981,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -25898,7 +26011,7 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
@@ -25907,13 +26020,13 @@
         </is>
       </c>
       <c r="N159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R159" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S159" t="inlineStr">
         <is>
@@ -25946,42 +26059,42 @@
       </c>
       <c r="AV159" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA159" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB159" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC159" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -26013,12 +26126,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -26043,7 +26156,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
@@ -26052,13 +26165,13 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R160" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0</v>
       </c>
       <c r="S160" t="inlineStr">
         <is>
@@ -26091,42 +26204,42 @@
       </c>
       <c r="AV160" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA160" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB160" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC160" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -26188,7 +26301,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
@@ -26303,12 +26416,12 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -26333,7 +26446,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
@@ -26342,13 +26455,13 @@
         </is>
       </c>
       <c r="N162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R162" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S162" t="inlineStr">
         <is>
@@ -26381,42 +26494,42 @@
       </c>
       <c r="AV162" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA162" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB162" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC162" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -26448,12 +26561,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -26478,7 +26591,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
@@ -26487,13 +26600,13 @@
         </is>
       </c>
       <c r="N163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R163" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0</v>
       </c>
       <c r="S163" t="inlineStr">
         <is>
@@ -26526,42 +26639,42 @@
       </c>
       <c r="AV163" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA163" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB163" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC163" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -26593,12 +26706,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -26623,12 +26736,12 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N164" t="n">
@@ -26671,42 +26784,42 @@
       </c>
       <c r="AV164" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA164" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB164" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC164" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -26738,12 +26851,12 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -26768,22 +26881,22 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R165" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S165" t="inlineStr">
         <is>
@@ -26816,42 +26929,42 @@
       </c>
       <c r="AV165" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA165" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB165" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC165" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -26883,12 +26996,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -26935,87 +27048,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U166" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_511_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA166" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO166" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP166" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ166" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR166" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS166" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_511_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS166" t="inlineStr"/>
       <c r="AT166" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU166" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV166" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA166" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB166" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC166" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -27042,217 +27136,526 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>Q热</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N167" t="n">
+        <v>0</v>
+      </c>
+      <c r="O167" t="n">
+        <v>0</v>
+      </c>
+      <c r="R167" t="n">
+        <v>0</v>
+      </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO167" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP167" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR167" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS167" t="inlineStr"/>
+      <c r="AT167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU167" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV167" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW167" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX167" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY167" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA167" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB167" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC167" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>q-fever</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>Q热</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N168" t="n">
+        <v>0</v>
+      </c>
+      <c r="O168" t="n">
+        <v>0</v>
+      </c>
+      <c r="R168" t="n">
+        <v>0</v>
+      </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_511_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO168" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP168" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ168" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR168" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS168" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_511_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT168" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU168" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV168" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW168" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX168" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY168" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA168" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB168" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC168" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>q-fever</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
           <t>source_series_observation</t>
         </is>
       </c>
-      <c r="F167" t="inlineStr">
+      <c r="F169" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G167" t="inlineStr">
+      <c r="G169" t="inlineStr">
         <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>D113</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>Q fever</t>
-        </is>
-      </c>
-      <c r="J167" t="inlineStr">
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
         <is>
           <t>Q热</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr">
+      <c r="K169" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L167" t="inlineStr">
+      <c r="L169" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="M167" t="inlineStr">
+      <c r="M169" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N167" t="n">
-        <v>0</v>
-      </c>
-      <c r="O167" t="n">
-        <v>0</v>
-      </c>
-      <c r="U167" t="inlineStr">
+      <c r="N169" t="n">
+        <v>0</v>
+      </c>
+      <c r="O169" t="n">
+        <v>0</v>
+      </c>
+      <c r="U169" t="inlineStr">
         <is>
           <t>SER_NO_FHI_511_MONTHLY</t>
         </is>
       </c>
-      <c r="V167" t="inlineStr">
+      <c r="V169" t="inlineStr">
         <is>
           <t>SER_NO_FHI_511_MONTHLY</t>
         </is>
       </c>
-      <c r="W167" t="inlineStr">
+      <c r="W169" t="inlineStr">
         <is>
           <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
-      <c r="X167" t="inlineStr">
+      <c r="X169" t="inlineStr">
         <is>
           <t>Q-feber</t>
         </is>
       </c>
-      <c r="Y167" t="inlineStr">
+      <c r="Y169" t="inlineStr">
         <is>
           <t>case_notifications</t>
         </is>
       </c>
-      <c r="Z167" t="inlineStr">
+      <c r="Z169" t="inlineStr">
         <is>
           <t>national_notifiable_disease_registry</t>
         </is>
       </c>
-      <c r="AA167" t="inlineStr">
+      <c r="AA169" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB167" t="inlineStr">
+      <c r="AB169" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="AC167" t="inlineStr">
+      <c r="AC169" t="inlineStr">
         <is>
           <t>country:NO:national</t>
         </is>
       </c>
-      <c r="AD167" t="inlineStr">
+      <c r="AD169" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE167" t="inlineStr">
+      <c r="AE169" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="AF167" t="inlineStr">
+      <c r="AF169" t="inlineStr">
         <is>
           <t>conditional</t>
         </is>
       </c>
-      <c r="AG167" t="inlineStr">
+      <c r="AG169" t="inlineStr">
         <is>
           <t>non_additive</t>
         </is>
       </c>
-      <c r="AH167" t="inlineStr">
+      <c r="AH169" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="AI167" t="inlineStr">
+      <c r="AI169" t="inlineStr">
         <is>
           <t>missing_is_unknown</t>
         </is>
       </c>
-      <c r="AJ167" t="inlineStr">
+      <c r="AJ169" t="inlineStr">
         <is>
           <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
-      <c r="AK167" t="inlineStr">
+      <c r="AK169" t="inlineStr">
         <is>
           <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
-      <c r="AM167" t="inlineStr">
+      <c r="AM169" t="inlineStr">
         <is>
           <t>provisional; raw; revised</t>
         </is>
       </c>
-      <c r="AN167" t="b">
+      <c r="AN169" t="b">
         <v>1</v>
       </c>
-      <c r="AO167" t="inlineStr">
+      <c r="AO169" t="inlineStr">
         <is>
           <t>series_registry</t>
         </is>
       </c>
-      <c r="AP167" t="inlineStr">
+      <c r="AP169" t="inlineStr">
         <is>
           <t>representative_series</t>
         </is>
       </c>
-      <c r="AQ167" t="inlineStr">
+      <c r="AQ169" t="inlineStr">
         <is>
           <t>parity</t>
         </is>
       </c>
-      <c r="AR167" t="inlineStr">
+      <c r="AR169" t="inlineStr">
         <is>
           <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
-      <c r="AS167" t="inlineStr">
+      <c r="AS169" t="inlineStr">
         <is>
           <t>SER_NO_FHI_511_MONTHLY</t>
         </is>
       </c>
-      <c r="AT167" t="n">
+      <c r="AT169" t="n">
         <v>2</v>
       </c>
-      <c r="AU167" t="inlineStr">
+      <c r="AU169" t="inlineStr">
         <is>
           <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
-      <c r="AV167" t="inlineStr">
+      <c r="AV169" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW167" t="inlineStr">
+      <c r="AW169" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX167" t="inlineStr">
+      <c r="AX169" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY167" t="inlineStr">
+      <c r="AY169" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ167" t="inlineStr">
+      <c r="AZ169" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA167" t="inlineStr">
+      <c r="BA169" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB167" t="inlineStr">
+      <c r="BB169" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC167" t="inlineStr">
+      <c r="BC169" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -27374,7 +27777,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="10">
@@ -27384,7 +27787,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="11">
@@ -27404,7 +27807,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d113/2026-2029.xlsx
+++ b/diseases/d113/2026-2029.xlsx
@@ -24072,13 +24072,13 @@
         </is>
       </c>
       <c r="N147" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="O147" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="R147" t="n">
-        <v>0.1432396609612718</v>
+        <v>0.1652765318783906</v>
       </c>
       <c r="S147" t="inlineStr">
         <is>
@@ -26996,12 +26996,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -27026,12 +27026,12 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N166" t="n">
@@ -27074,42 +27074,42 @@
       </c>
       <c r="AV166" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA166" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB166" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC166" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -27141,12 +27141,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -27219,42 +27219,42 @@
       </c>
       <c r="AV167" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA167" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB167" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC167" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -27286,12 +27286,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -27338,87 +27338,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U168" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_511_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA168" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO168" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP168" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ168" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR168" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS168" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_511_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS168" t="inlineStr"/>
       <c r="AT168" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU168" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV168" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ168" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA168" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB168" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC168" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -27445,7 +27426,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -27494,98 +27475,23 @@
       <c r="O169" t="n">
         <v>0</v>
       </c>
+      <c r="R169" t="n">
+        <v>0</v>
+      </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U169" t="inlineStr">
         <is>
           <t>SER_NO_FHI_511_MONTHLY</t>
         </is>
       </c>
-      <c r="V169" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_511_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W169" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X169" t="inlineStr">
-        <is>
-          <t>Q-feber</t>
-        </is>
-      </c>
-      <c r="Y169" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z169" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA169" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB169" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC169" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD169" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE169" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF169" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG169" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH169" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI169" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ169" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK169" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM169" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN169" t="b">
-        <v>1</v>
       </c>
       <c r="AO169" t="inlineStr">
         <is>
@@ -27656,6 +27562,245 @@
         </is>
       </c>
       <c r="BC169" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>q-fever</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>Q热</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N170" t="n">
+        <v>0</v>
+      </c>
+      <c r="O170" t="n">
+        <v>0</v>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_511_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V170" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_511_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W170" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X170" t="inlineStr">
+        <is>
+          <t>Q-feber</t>
+        </is>
+      </c>
+      <c r="Y170" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z170" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB170" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD170" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE170" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF170" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG170" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH170" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI170" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ170" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK170" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM170" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN170" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO170" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP170" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ170" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR170" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS170" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_511_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT170" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU170" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV170" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW170" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX170" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY170" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA170" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB170" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC170" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -27777,7 +27922,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10">
@@ -27787,7 +27932,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11">
@@ -27839,7 +27984,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>763</v>
+        <v>769</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d113/2026-2029.xlsx
+++ b/diseases/d113/2026-2029.xlsx
@@ -20245,13 +20245,13 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O122" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R122" t="n">
-        <v>0.1946590264345489</v>
+        <v>0.1983318382540687</v>
       </c>
       <c r="S122" t="inlineStr">
         <is>
@@ -24072,13 +24072,13 @@
         </is>
       </c>
       <c r="N147" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O147" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="R147" t="n">
-        <v>0.1652765318783906</v>
+        <v>0.1726221555174302</v>
       </c>
       <c r="S147" t="inlineStr">
         <is>
@@ -25069,13 +25069,13 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O154" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R154" t="n">
-        <v>0.01744172931412841</v>
+        <v>0.01937969923792046</v>
       </c>
       <c r="S154" t="inlineStr">
         <is>
@@ -27325,13 +27325,13 @@
         </is>
       </c>
       <c r="N168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R168" t="n">
-        <v>0</v>
+        <v>0.001937969923792046</v>
       </c>
       <c r="S168" t="inlineStr">
         <is>
@@ -27984,7 +27984,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>769</v>
+        <v>774</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d113/2026-2029.xlsx
+++ b/diseases/d113/2026-2029.xlsx
@@ -24072,13 +24072,13 @@
         </is>
       </c>
       <c r="N147" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O147" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="R147" t="n">
-        <v>0.1726221555174302</v>
+        <v>0.1762949673369499</v>
       </c>
       <c r="S147" t="inlineStr">
         <is>
@@ -27803,6 +27803,151 @@
       <c r="BC170" t="inlineStr">
         <is>
           <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>q-fever</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>Q热</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N171" t="n">
+        <v>4</v>
+      </c>
+      <c r="O171" t="n">
+        <v>4</v>
+      </c>
+      <c r="R171" t="n">
+        <v>0.001146015253107754</v>
+      </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO171" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP171" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR171" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS171" t="inlineStr"/>
+      <c r="AT171" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU171" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV171" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW171" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX171" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY171" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA171" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB171" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC171" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -27839,7 +27984,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -27922,7 +28067,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="10">
@@ -27932,7 +28077,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="11">
@@ -27984,7 +28129,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>774</v>
+        <v>779</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d113/2026-2029.xlsx
+++ b/diseases/d113/2026-2029.xlsx
@@ -4019,10 +4019,10 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -4175,10 +4175,10 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U23" t="inlineStr">
         <is>
@@ -21487,12 +21487,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -21526,81 +21526,92 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="O131" t="n">
-        <v>10</v>
-      </c>
-      <c r="R131" t="n">
-        <v>0.1110149228479591</v>
+        <v>2</v>
       </c>
       <c r="S131" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_Q_FEVER_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO131" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR131" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS131" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ131" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS131" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_Q_FEVER_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV131" t="inlineStr">
         <is>
-          <t>foph_idd</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Switzerland FOPH IDD</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
         <is>
-          <t>rest_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>foph_idd</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA131" t="inlineStr">
         <is>
-          <t>Switzerland FOPH IDD</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB131" t="inlineStr">
         <is>
-          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC131" t="inlineStr">
         <is>
-          <t>rest_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -21627,17 +21638,17 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -21671,81 +21682,170 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O132" t="n">
-        <v>0</v>
-      </c>
-      <c r="R132" t="n">
-        <v>0</v>
-      </c>
-      <c r="S132" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_Q_FEVER_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_Q_FEVER_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X132" t="inlineStr">
+        <is>
+          <t>Q Fever</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD132" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE132" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF132" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG132" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH132" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI132" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ132" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK132" t="inlineStr">
+        <is>
+          <t>PHO IDTO current-year monthly preliminary q fever notifications; confirmed cases only under the July 2026 technical notes.</t>
+        </is>
+      </c>
+      <c r="AM132" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN132" t="b">
+        <v>1</v>
       </c>
       <c r="AO132" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP132" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR132" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS132" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ132" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS132" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_Q_FEVER_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU132" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV132" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA132" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB132" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC132" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -21777,12 +21877,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -21816,13 +21916,13 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="O133" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="R133" t="n">
-        <v>0.02325563908550455</v>
+        <v>0.1110149228479591</v>
       </c>
       <c r="S133" t="inlineStr">
         <is>
@@ -21855,42 +21955,42 @@
       </c>
       <c r="AV133" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>rest_api</t>
         </is>
       </c>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="BA133" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="BB133" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="BC133" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>rest_api</t>
         </is>
       </c>
     </row>
@@ -21922,12 +22022,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -21974,87 +22074,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U134" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_511_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA134" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO134" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP134" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ134" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR134" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS134" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_511_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS134" t="inlineStr"/>
       <c r="AT134" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU134" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV134" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA134" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB134" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC134" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -22081,17 +22162,17 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -22125,175 +22206,81 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O135" t="n">
-        <v>0</v>
-      </c>
-      <c r="U135" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_511_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V135" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_511_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W135" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X135" t="inlineStr">
-        <is>
-          <t>Q-feber</t>
-        </is>
-      </c>
-      <c r="Y135" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z135" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA135" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB135" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD135" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE135" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF135" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG135" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH135" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI135" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ135" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK135" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM135" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN135" t="b">
-        <v>1</v>
+        <v>12</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.02325563908550455</v>
+      </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO135" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP135" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ135" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR135" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS135" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_511_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS135" t="inlineStr"/>
       <c r="AT135" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU135" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV135" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA135" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB135" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC135" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -22325,12 +22312,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -22364,13 +22351,13 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R136" t="n">
-        <v>0.009344880428283346</v>
+        <v>0</v>
       </c>
       <c r="S136" t="inlineStr">
         <is>
@@ -22379,7 +22366,7 @@
       </c>
       <c r="U136" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
+          <t>SER_NO_FHI_511_MONTHLY</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -22409,7 +22396,7 @@
       </c>
       <c r="AS136" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
+          <t>SER_NO_FHI_511_MONTHLY</t>
         </is>
       </c>
       <c r="AT136" t="n">
@@ -22422,42 +22409,42 @@
       </c>
       <c r="AV136" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA136" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB136" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC136" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -22489,12 +22476,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -22528,24 +22515,24 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U137" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
+          <t>SER_NO_FHI_511_MONTHLY</t>
         </is>
       </c>
       <c r="V137" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
+          <t>SER_NO_FHI_511_MONTHLY</t>
         </is>
       </c>
       <c r="W137" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X137" t="inlineStr">
@@ -22575,7 +22562,7 @@
       </c>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD137" t="inlineStr">
@@ -22610,17 +22597,17 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN137" t="b">
@@ -22648,7 +22635,7 @@
       </c>
       <c r="AS137" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
+          <t>SER_NO_FHI_511_MONTHLY</t>
         </is>
       </c>
       <c r="AT137" t="n">
@@ -22661,42 +22648,42 @@
       </c>
       <c r="AV137" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA137" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB137" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC137" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -22728,12 +22715,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -22758,7 +22745,7 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
@@ -22767,81 +22754,100 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R138" t="n">
-        <v>0</v>
+        <v>0.009344880428283346</v>
       </c>
       <c r="S138" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO138" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP138" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ138" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR138" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS138" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS138" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
+        </is>
+      </c>
       <c r="AT138" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU138" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV138" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA138" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB138" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC138" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -22868,17 +22874,17 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -22903,7 +22909,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
@@ -22912,81 +22918,175 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O139" t="n">
-        <v>0</v>
-      </c>
-      <c r="R139" t="n">
-        <v>0</v>
-      </c>
-      <c r="S139" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X139" t="inlineStr">
+        <is>
+          <t>Q-feber</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD139" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE139" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF139" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG139" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH139" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI139" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ139" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK139" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM139" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN139" t="b">
+        <v>1</v>
       </c>
       <c r="AO139" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP139" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ139" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR139" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS139" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS139" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
+        </is>
+      </c>
       <c r="AT139" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU139" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV139" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA139" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB139" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC139" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -23048,7 +23148,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -23193,7 +23293,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
@@ -23202,13 +23302,13 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R141" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0</v>
       </c>
       <c r="S141" t="inlineStr">
         <is>
@@ -23338,7 +23438,7 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
@@ -23483,7 +23583,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -23492,13 +23592,13 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O143" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R143" t="n">
-        <v>0.0005730076265538771</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S143" t="inlineStr">
         <is>
@@ -23628,7 +23728,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -23773,7 +23873,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -23782,13 +23882,13 @@
         </is>
       </c>
       <c r="N145" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O145" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R145" t="n">
-        <v>0</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S145" t="inlineStr">
         <is>
@@ -23918,7 +24018,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -24033,12 +24133,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -24063,22 +24163,22 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N147" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="O147" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="R147" t="n">
-        <v>0.1762949673369499</v>
+        <v>0</v>
       </c>
       <c r="S147" t="inlineStr">
         <is>
@@ -24111,42 +24211,42 @@
       </c>
       <c r="AV147" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA147" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB147" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC147" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -24178,12 +24278,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -24208,12 +24308,12 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N148" t="n">
@@ -24222,9 +24322,12 @@
       <c r="O148" t="n">
         <v>0</v>
       </c>
+      <c r="R148" t="n">
+        <v>0</v>
+      </c>
       <c r="S148" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AO148" t="inlineStr">
@@ -24253,42 +24356,42 @@
       </c>
       <c r="AV148" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA148" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB148" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC148" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -24320,12 +24423,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -24359,14 +24462,17 @@
         </is>
       </c>
       <c r="N149" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="O149" t="n">
-        <v>12</v>
+        <v>48</v>
+      </c>
+      <c r="R149" t="n">
+        <v>0.1762949673369499</v>
       </c>
       <c r="S149" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AO149" t="inlineStr">
@@ -24400,12 +24506,12 @@
       </c>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
@@ -24420,12 +24526,12 @@
       </c>
       <c r="BA149" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB149" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC149" t="inlineStr">
@@ -24462,12 +24568,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -24501,10 +24607,10 @@
         </is>
       </c>
       <c r="N150" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O150" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="S150" t="inlineStr">
         <is>
@@ -24542,7 +24648,7 @@
       </c>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
@@ -24562,7 +24668,7 @@
       </c>
       <c r="BA150" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB150" t="inlineStr">
@@ -24604,12 +24710,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -24643,10 +24749,10 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O151" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="S151" t="inlineStr">
         <is>
@@ -24684,7 +24790,7 @@
       </c>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
@@ -24704,7 +24810,7 @@
       </c>
       <c r="BA151" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB151" t="inlineStr">
@@ -24746,12 +24852,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -24785,10 +24891,10 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O152" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="S152" t="inlineStr">
         <is>
@@ -24826,7 +24932,7 @@
       </c>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
@@ -24846,7 +24952,7 @@
       </c>
       <c r="BA152" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB152" t="inlineStr">
@@ -24888,12 +24994,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -24968,7 +25074,7 @@
       </c>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
@@ -24988,7 +25094,7 @@
       </c>
       <c r="BA153" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB153" t="inlineStr">
@@ -25030,12 +25136,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -25069,17 +25175,14 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O154" t="n">
-        <v>10</v>
-      </c>
-      <c r="R154" t="n">
-        <v>0.01937969923792046</v>
+        <v>0</v>
       </c>
       <c r="S154" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO154" t="inlineStr">
@@ -25108,42 +25211,42 @@
       </c>
       <c r="AV154" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA154" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB154" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC154" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -25175,12 +25278,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -25219,95 +25322,73 @@
       <c r="O155" t="n">
         <v>0</v>
       </c>
-      <c r="R155" t="n">
-        <v>0</v>
-      </c>
       <c r="S155" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U155" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_511_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA155" t="inlineStr">
-        <is>
-          <t>monthly</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO155" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ155" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR155" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS155" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_511_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS155" t="inlineStr"/>
       <c r="AT155" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU155" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV155" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA155" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB155" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC155" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -25334,17 +25415,17 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -25378,175 +25459,81 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O156" t="n">
-        <v>0</v>
-      </c>
-      <c r="U156" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_511_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V156" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_511_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W156" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X156" t="inlineStr">
-        <is>
-          <t>Q-feber</t>
-        </is>
-      </c>
-      <c r="Y156" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z156" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA156" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB156" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC156" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD156" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE156" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF156" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG156" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH156" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI156" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ156" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK156" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM156" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN156" t="b">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="R156" t="n">
+        <v>0.01937969923792046</v>
+      </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO156" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP156" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ156" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR156" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS156" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_511_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS156" t="inlineStr"/>
       <c r="AT156" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU156" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV156" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA156" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB156" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC156" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -25578,12 +25565,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -25632,7 +25619,7 @@
       </c>
       <c r="U157" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
+          <t>SER_NO_FHI_511_MONTHLY</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -25662,7 +25649,7 @@
       </c>
       <c r="AS157" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
+          <t>SER_NO_FHI_511_MONTHLY</t>
         </is>
       </c>
       <c r="AT157" t="n">
@@ -25675,42 +25662,42 @@
       </c>
       <c r="AV157" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA157" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB157" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC157" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -25742,12 +25729,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -25788,17 +25775,17 @@
       </c>
       <c r="U158" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
+          <t>SER_NO_FHI_511_MONTHLY</t>
         </is>
       </c>
       <c r="V158" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
+          <t>SER_NO_FHI_511_MONTHLY</t>
         </is>
       </c>
       <c r="W158" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X158" t="inlineStr">
@@ -25828,7 +25815,7 @@
       </c>
       <c r="AC158" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD158" t="inlineStr">
@@ -25863,17 +25850,17 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK158" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM158" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN158" t="b">
@@ -25901,7 +25888,7 @@
       </c>
       <c r="AS158" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
+          <t>SER_NO_FHI_511_MONTHLY</t>
         </is>
       </c>
       <c r="AT158" t="n">
@@ -25914,42 +25901,42 @@
       </c>
       <c r="AV158" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA158" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB158" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC158" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -25981,12 +25968,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -26020,81 +26007,100 @@
         </is>
       </c>
       <c r="N159" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O159" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R159" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0</v>
       </c>
       <c r="S159" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO159" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP159" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ159" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR159" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS159" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS159" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
+        </is>
+      </c>
       <c r="AT159" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU159" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV159" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA159" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB159" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC159" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -26121,17 +26127,17 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -26156,7 +26162,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
@@ -26170,76 +26176,170 @@
       <c r="O160" t="n">
         <v>0</v>
       </c>
-      <c r="R160" t="n">
-        <v>0</v>
-      </c>
-      <c r="S160" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
+        </is>
+      </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
+        </is>
+      </c>
+      <c r="W160" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X160" t="inlineStr">
+        <is>
+          <t>Q-feber</t>
+        </is>
+      </c>
+      <c r="Y160" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB160" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD160" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE160" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF160" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG160" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH160" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI160" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ160" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK160" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM160" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN160" t="b">
+        <v>1</v>
       </c>
       <c r="AO160" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP160" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ160" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR160" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS160" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS160" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
+        </is>
+      </c>
       <c r="AT160" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU160" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV160" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA160" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB160" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC160" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -26271,12 +26371,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -26301,7 +26401,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
@@ -26310,13 +26410,13 @@
         </is>
       </c>
       <c r="N161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R161" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S161" t="inlineStr">
         <is>
@@ -26349,42 +26449,42 @@
       </c>
       <c r="AV161" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA161" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB161" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC161" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -26416,12 +26516,12 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -26446,7 +26546,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
@@ -26455,13 +26555,13 @@
         </is>
       </c>
       <c r="N162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R162" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0</v>
       </c>
       <c r="S162" t="inlineStr">
         <is>
@@ -26494,42 +26594,42 @@
       </c>
       <c r="AV162" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA162" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB162" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC162" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -26591,7 +26691,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
@@ -26706,12 +26806,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -26736,7 +26836,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
@@ -26745,13 +26845,13 @@
         </is>
       </c>
       <c r="N164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R164" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S164" t="inlineStr">
         <is>
@@ -26784,42 +26884,42 @@
       </c>
       <c r="AV164" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA164" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB164" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC164" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -26851,12 +26951,12 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -26881,7 +26981,7 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
@@ -26890,13 +26990,13 @@
         </is>
       </c>
       <c r="N165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R165" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0</v>
       </c>
       <c r="S165" t="inlineStr">
         <is>
@@ -26929,42 +27029,42 @@
       </c>
       <c r="AV165" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA165" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB165" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC165" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -27026,7 +27126,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
@@ -27141,12 +27241,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -27171,22 +27271,22 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R167" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S167" t="inlineStr">
         <is>
@@ -27219,42 +27319,42 @@
       </c>
       <c r="AV167" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA167" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB167" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC167" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -27286,12 +27386,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -27316,22 +27416,22 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R168" t="n">
-        <v>0.001937969923792046</v>
+        <v>0</v>
       </c>
       <c r="S168" t="inlineStr">
         <is>
@@ -27364,42 +27464,42 @@
       </c>
       <c r="AV168" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ168" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA168" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB168" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC168" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -27431,12 +27531,12 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -27483,87 +27583,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U169" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_511_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA169" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO169" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP169" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ169" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR169" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS169" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_511_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS169" t="inlineStr"/>
       <c r="AT169" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU169" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV169" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ169" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA169" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB169" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC169" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -27590,17 +27671,17 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -27634,175 +27715,81 @@
         </is>
       </c>
       <c r="N170" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O170" t="n">
-        <v>0</v>
-      </c>
-      <c r="U170" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_511_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V170" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_511_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W170" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X170" t="inlineStr">
-        <is>
-          <t>Q-feber</t>
-        </is>
-      </c>
-      <c r="Y170" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z170" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA170" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB170" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC170" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD170" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE170" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF170" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG170" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH170" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI170" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ170" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK170" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM170" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN170" t="b">
         <v>1</v>
       </c>
+      <c r="R170" t="n">
+        <v>0.001937969923792046</v>
+      </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AO170" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP170" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ170" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR170" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS170" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_511_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS170" t="inlineStr"/>
       <c r="AT170" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU170" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV170" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ170" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA170" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB170" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC170" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -27834,118 +27821,521 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>Q热</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N171" t="n">
+        <v>0</v>
+      </c>
+      <c r="O171" t="n">
+        <v>0</v>
+      </c>
+      <c r="R171" t="n">
+        <v>0</v>
+      </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_511_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO171" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP171" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ171" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR171" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS171" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_511_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT171" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU171" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV171" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW171" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX171" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY171" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA171" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB171" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC171" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>q-fever</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>Q热</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N172" t="n">
+        <v>0</v>
+      </c>
+      <c r="O172" t="n">
+        <v>0</v>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_511_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V172" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_511_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W172" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X172" t="inlineStr">
+        <is>
+          <t>Q-feber</t>
+        </is>
+      </c>
+      <c r="Y172" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z172" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB172" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC172" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD172" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE172" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF172" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG172" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH172" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI172" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ172" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK172" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM172" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN172" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO172" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP172" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ172" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR172" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS172" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_511_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT172" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU172" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV172" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW172" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX172" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY172" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA172" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB172" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC172" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>q-fever</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G171" t="inlineStr">
+      <c r="G173" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>D113</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>Q fever</t>
-        </is>
-      </c>
-      <c r="J171" t="inlineStr">
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
         <is>
           <t>Q热</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr">
+      <c r="K173" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L171" t="inlineStr">
+      <c r="L173" t="inlineStr">
         <is>
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="M171" t="inlineStr">
+      <c r="M173" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N171" t="n">
+      <c r="N173" t="n">
         <v>4</v>
       </c>
-      <c r="O171" t="n">
+      <c r="O173" t="n">
         <v>4</v>
       </c>
-      <c r="R171" t="n">
+      <c r="R173" t="n">
         <v>0.001146015253107754</v>
       </c>
-      <c r="S171" t="inlineStr">
+      <c r="S173" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO171" t="inlineStr">
+      <c r="AO173" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP171" t="inlineStr">
+      <c r="AP173" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR171" t="inlineStr">
+      <c r="AR173" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS171" t="inlineStr"/>
-      <c r="AT171" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU171" t="inlineStr">
+      <c r="AS173" t="inlineStr"/>
+      <c r="AT173" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU173" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV171" t="inlineStr">
+      <c r="AV173" t="inlineStr">
         <is>
           <t>nndss_api</t>
         </is>
       </c>
-      <c r="AW171" t="inlineStr">
+      <c r="AW173" t="inlineStr">
         <is>
           <t>US CDC NNDSS</t>
         </is>
       </c>
-      <c r="AX171" t="inlineStr">
+      <c r="AX173" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
-      <c r="AY171" t="inlineStr">
+      <c r="AY173" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="AZ171" t="inlineStr">
+      <c r="AZ173" t="inlineStr">
         <is>
           <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
-      <c r="BA171" t="inlineStr">
+      <c r="BA173" t="inlineStr">
         <is>
           <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
-      <c r="BB171" t="inlineStr">
+      <c r="BB173" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
-      <c r="BC171" t="inlineStr">
+      <c r="BC173" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -28067,7 +28457,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="10">
@@ -28077,7 +28467,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11">
@@ -28097,7 +28487,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13">
@@ -28129,7 +28519,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>779</v>
+        <v>782</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d113/2026-2029.xlsx
+++ b/diseases/d113/2026-2029.xlsx
@@ -24462,13 +24462,13 @@
         </is>
       </c>
       <c r="N149" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="O149" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="R149" t="n">
-        <v>0.1762949673369499</v>
+        <v>0.1873134027955093</v>
       </c>
       <c r="S149" t="inlineStr">
         <is>
@@ -28519,7 +28519,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>782</v>
+        <v>785</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d113/2026-2029.xlsx
+++ b/diseases/d113/2026-2029.xlsx
@@ -24462,13 +24462,13 @@
         </is>
       </c>
       <c r="N149" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O149" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="R149" t="n">
-        <v>0.1873134027955093</v>
+        <v>0.1946590264345489</v>
       </c>
       <c r="S149" t="inlineStr">
         <is>
@@ -28519,7 +28519,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>785</v>
+        <v>787</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d113/2026-2029.xlsx
+++ b/diseases/d113/2026-2029.xlsx
@@ -28341,6 +28341,151 @@
         </is>
       </c>
     </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>q-fever</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>Q热</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N174" t="n">
+        <v>0</v>
+      </c>
+      <c r="O174" t="n">
+        <v>0</v>
+      </c>
+      <c r="R174" t="n">
+        <v>0</v>
+      </c>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO174" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP174" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR174" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS174" t="inlineStr"/>
+      <c r="AT174" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU174" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV174" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW174" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX174" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY174" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA174" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB174" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC174" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -28374,7 +28519,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -28457,7 +28602,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="10">
@@ -28467,7 +28612,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d113/2026-2029.xlsx
+++ b/diseases/d113/2026-2029.xlsx
@@ -20245,13 +20245,13 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="O122" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="R122" t="n">
-        <v>0.1983318382540687</v>
+        <v>0.2020046500735885</v>
       </c>
       <c r="S122" t="inlineStr">
         <is>
@@ -24462,13 +24462,13 @@
         </is>
       </c>
       <c r="N149" t="n">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="O149" t="n">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="R149" t="n">
-        <v>0.1946590264345489</v>
+        <v>0.227714332810227</v>
       </c>
       <c r="S149" t="inlineStr">
         <is>
@@ -27715,13 +27715,13 @@
         </is>
       </c>
       <c r="N170" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O170" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R170" t="n">
-        <v>0.001937969923792046</v>
+        <v>0.003875939847584092</v>
       </c>
       <c r="S170" t="inlineStr">
         <is>
@@ -28664,7 +28664,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>787</v>
+        <v>798</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d113/2026-2029.xlsx
+++ b/diseases/d113/2026-2029.xlsx
@@ -20245,13 +20245,13 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="O122" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="R122" t="n">
-        <v>0.2020046500735885</v>
+        <v>0.2056774618931082</v>
       </c>
       <c r="S122" t="inlineStr">
         <is>
@@ -28664,7 +28664,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>798</v>
+        <v>799</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d113/2026-2029.xlsx
+++ b/diseases/d113/2026-2029.xlsx
@@ -24462,13 +24462,13 @@
         </is>
       </c>
       <c r="N149" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="O149" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="R149" t="n">
-        <v>0.227714332810227</v>
+        <v>0.2350599564492666</v>
       </c>
       <c r="S149" t="inlineStr">
         <is>
@@ -25420,12 +25420,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -25459,13 +25459,13 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O156" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R156" t="n">
-        <v>0.01937969923792046</v>
+        <v>0</v>
       </c>
       <c r="S156" t="inlineStr">
         <is>
@@ -25498,42 +25498,42 @@
       </c>
       <c r="AV156" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA156" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB156" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC156" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -25565,12 +25565,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -25604,100 +25604,81 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O157" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R157" t="n">
-        <v>0</v>
+        <v>0.01937969923792046</v>
       </c>
       <c r="S157" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U157" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_511_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA157" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO157" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP157" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ157" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR157" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS157" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_511_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS157" t="inlineStr"/>
       <c r="AT157" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU157" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV157" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA157" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB157" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC157" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -25724,7 +25705,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -25773,98 +25754,23 @@
       <c r="O158" t="n">
         <v>0</v>
       </c>
+      <c r="R158" t="n">
+        <v>0</v>
+      </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U158" t="inlineStr">
         <is>
           <t>SER_NO_FHI_511_MONTHLY</t>
         </is>
       </c>
-      <c r="V158" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_511_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W158" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X158" t="inlineStr">
-        <is>
-          <t>Q-feber</t>
-        </is>
-      </c>
-      <c r="Y158" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z158" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB158" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC158" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD158" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE158" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF158" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG158" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH158" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI158" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ158" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK158" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM158" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN158" t="b">
-        <v>1</v>
       </c>
       <c r="AO158" t="inlineStr">
         <is>
@@ -25963,17 +25869,17 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -26012,17 +25918,34 @@
       <c r="O159" t="n">
         <v>0</v>
       </c>
-      <c r="R159" t="n">
-        <v>0</v>
-      </c>
-      <c r="S159" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U159" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
+          <t>SER_NO_FHI_511_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_511_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X159" t="inlineStr">
+        <is>
+          <t>Q-feber</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -26030,6 +25953,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB159" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD159" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE159" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF159" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG159" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH159" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI159" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ159" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK159" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM159" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN159" t="b">
+        <v>1</v>
+      </c>
       <c r="AO159" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -26052,7 +26033,7 @@
       </c>
       <c r="AS159" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
+          <t>SER_NO_FHI_511_MONTHLY</t>
         </is>
       </c>
       <c r="AT159" t="n">
@@ -26065,42 +26046,42 @@
       </c>
       <c r="AV159" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA159" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB159" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC159" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -26127,7 +26108,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -26176,98 +26157,23 @@
       <c r="O160" t="n">
         <v>0</v>
       </c>
+      <c r="R160" t="n">
+        <v>0</v>
+      </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U160" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
         </is>
       </c>
-      <c r="V160" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
-        </is>
-      </c>
-      <c r="W160" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X160" t="inlineStr">
-        <is>
-          <t>Q-feber</t>
-        </is>
-      </c>
-      <c r="Y160" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z160" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB160" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC160" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD160" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE160" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF160" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG160" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH160" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI160" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ160" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK160" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
-        </is>
-      </c>
-      <c r="AM160" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN160" t="b">
-        <v>1</v>
       </c>
       <c r="AO160" t="inlineStr">
         <is>
@@ -26366,17 +26272,17 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -26410,81 +26316,175 @@
         </is>
       </c>
       <c r="N161" t="n">
+        <v>0</v>
+      </c>
+      <c r="O161" t="n">
+        <v>0</v>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
+        </is>
+      </c>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
+        </is>
+      </c>
+      <c r="W161" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X161" t="inlineStr">
+        <is>
+          <t>Q-feber</t>
+        </is>
+      </c>
+      <c r="Y161" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z161" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB161" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC161" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD161" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE161" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF161" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG161" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH161" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI161" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ161" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK161" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM161" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN161" t="b">
         <v>1</v>
       </c>
-      <c r="O161" t="n">
-        <v>1</v>
-      </c>
-      <c r="R161" t="n">
-        <v>0.0002865038132769385</v>
-      </c>
-      <c r="S161" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AO161" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP161" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ161" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR161" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS161" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS161" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
+        </is>
+      </c>
       <c r="AT161" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU161" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV161" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA161" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB161" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC161" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -26516,12 +26516,12 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -26546,7 +26546,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
@@ -26555,13 +26555,13 @@
         </is>
       </c>
       <c r="N162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R162" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S162" t="inlineStr">
         <is>
@@ -26594,42 +26594,42 @@
       </c>
       <c r="AV162" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA162" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB162" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC162" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -26691,7 +26691,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
@@ -26806,12 +26806,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -26836,7 +26836,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
@@ -26845,13 +26845,13 @@
         </is>
       </c>
       <c r="N164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R164" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0</v>
       </c>
       <c r="S164" t="inlineStr">
         <is>
@@ -26884,42 +26884,42 @@
       </c>
       <c r="AV164" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA164" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB164" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC164" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -26951,12 +26951,12 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -26981,7 +26981,7 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
@@ -26990,13 +26990,13 @@
         </is>
       </c>
       <c r="N165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R165" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S165" t="inlineStr">
         <is>
@@ -27029,42 +27029,42 @@
       </c>
       <c r="AV165" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA165" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB165" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC165" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -27126,7 +27126,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
@@ -27241,12 +27241,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -27271,7 +27271,7 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
@@ -27280,13 +27280,13 @@
         </is>
       </c>
       <c r="N167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R167" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0</v>
       </c>
       <c r="S167" t="inlineStr">
         <is>
@@ -27319,42 +27319,42 @@
       </c>
       <c r="AV167" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA167" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB167" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC167" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -27386,12 +27386,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -27416,7 +27416,7 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
@@ -27425,13 +27425,13 @@
         </is>
       </c>
       <c r="N168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R168" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S168" t="inlineStr">
         <is>
@@ -27464,42 +27464,42 @@
       </c>
       <c r="AV168" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ168" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA168" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB168" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC168" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -27531,12 +27531,12 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -27561,12 +27561,12 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N169" t="n">
@@ -27609,42 +27609,42 @@
       </c>
       <c r="AV169" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ169" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA169" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB169" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC169" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -27676,12 +27676,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -27715,13 +27715,13 @@
         </is>
       </c>
       <c r="N170" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O170" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R170" t="n">
-        <v>0.003875939847584092</v>
+        <v>0</v>
       </c>
       <c r="S170" t="inlineStr">
         <is>
@@ -27754,42 +27754,42 @@
       </c>
       <c r="AV170" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ170" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA170" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB170" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC170" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -27821,12 +27821,12 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -27860,100 +27860,81 @@
         </is>
       </c>
       <c r="N171" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O171" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R171" t="n">
-        <v>0</v>
+        <v>0.003875939847584092</v>
       </c>
       <c r="S171" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U171" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_511_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA171" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO171" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP171" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ171" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR171" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS171" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_511_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS171" t="inlineStr"/>
       <c r="AT171" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU171" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV171" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ171" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA171" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB171" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC171" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -27980,7 +27961,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -28029,98 +28010,23 @@
       <c r="O172" t="n">
         <v>0</v>
       </c>
+      <c r="R172" t="n">
+        <v>0</v>
+      </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U172" t="inlineStr">
         <is>
           <t>SER_NO_FHI_511_MONTHLY</t>
         </is>
       </c>
-      <c r="V172" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_511_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W172" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X172" t="inlineStr">
-        <is>
-          <t>Q-feber</t>
-        </is>
-      </c>
-      <c r="Y172" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z172" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA172" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB172" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC172" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD172" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE172" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF172" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG172" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH172" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI172" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ172" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK172" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM172" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN172" t="b">
-        <v>1</v>
       </c>
       <c r="AO172" t="inlineStr">
         <is>
@@ -28219,17 +28125,17 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -28254,7 +28160,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -28263,81 +28169,175 @@
         </is>
       </c>
       <c r="N173" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O173" t="n">
-        <v>4</v>
-      </c>
-      <c r="R173" t="n">
-        <v>0.001146015253107754</v>
-      </c>
-      <c r="S173" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_511_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V173" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_511_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W173" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X173" t="inlineStr">
+        <is>
+          <t>Q-feber</t>
+        </is>
+      </c>
+      <c r="Y173" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z173" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB173" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC173" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD173" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE173" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF173" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG173" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH173" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI173" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ173" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK173" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM173" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN173" t="b">
+        <v>1</v>
       </c>
       <c r="AO173" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP173" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ173" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR173" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS173" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS173" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_511_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT173" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU173" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV173" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA173" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB173" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC173" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -28369,12 +28369,12 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -28399,7 +28399,7 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
@@ -28408,13 +28408,13 @@
         </is>
       </c>
       <c r="N174" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O174" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R174" t="n">
-        <v>0</v>
+        <v>0.001146015253107754</v>
       </c>
       <c r="S174" t="inlineStr">
         <is>
@@ -28447,42 +28447,477 @@
       </c>
       <c r="AV174" t="inlineStr">
         <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW174" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX174" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY174" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA174" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB174" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC174" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>q-fever</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>Q热</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N175" t="n">
+        <v>0</v>
+      </c>
+      <c r="O175" t="n">
+        <v>0</v>
+      </c>
+      <c r="R175" t="n">
+        <v>0</v>
+      </c>
+      <c r="S175" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO175" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP175" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR175" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS175" t="inlineStr"/>
+      <c r="AT175" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU175" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV175" t="inlineStr">
+        <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW174" t="inlineStr">
+      <c r="AW175" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX174" t="inlineStr">
+      <c r="AX175" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY174" t="inlineStr">
+      <c r="AY175" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ174" t="inlineStr">
+      <c r="AZ175" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA174" t="inlineStr">
+      <c r="BA175" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB174" t="inlineStr">
+      <c r="BB175" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC174" t="inlineStr">
+      <c r="BC175" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>q-fever</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>Q热</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N176" t="n">
+        <v>0</v>
+      </c>
+      <c r="O176" t="n">
+        <v>0</v>
+      </c>
+      <c r="R176" t="n">
+        <v>0</v>
+      </c>
+      <c r="S176" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO176" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP176" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR176" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS176" t="inlineStr"/>
+      <c r="AT176" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU176" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV176" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW176" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX176" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY176" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA176" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB176" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC176" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>q-fever</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>Q热</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N177" t="n">
+        <v>1</v>
+      </c>
+      <c r="O177" t="n">
+        <v>1</v>
+      </c>
+      <c r="R177" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
+      <c r="S177" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO177" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP177" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR177" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS177" t="inlineStr"/>
+      <c r="AT177" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU177" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV177" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW177" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX177" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY177" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA177" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB177" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC177" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -28519,7 +28954,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -28602,7 +29037,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="10">
@@ -28612,7 +29047,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>173</v>
+        <v>176</v>
       </c>
     </row>
     <row r="11">
@@ -28664,7 +29099,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>799</v>
+        <v>802</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d113/2026-2029.xlsx
+++ b/diseases/d113/2026-2029.xlsx
@@ -24462,13 +24462,13 @@
         </is>
       </c>
       <c r="N149" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="O149" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="R149" t="n">
-        <v>0.2350599564492666</v>
+        <v>0.246078391907826</v>
       </c>
       <c r="S149" t="inlineStr">
         <is>
@@ -27715,13 +27715,13 @@
         </is>
       </c>
       <c r="N170" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="O170" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="R170" t="n">
-        <v>0</v>
+        <v>0.1101843545855937</v>
       </c>
       <c r="S170" t="inlineStr">
         <is>
@@ -27860,13 +27860,13 @@
         </is>
       </c>
       <c r="N171" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O171" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R171" t="n">
-        <v>0.003875939847584092</v>
+        <v>0.005813909771376137</v>
       </c>
       <c r="S171" t="inlineStr">
         <is>
@@ -28918,6 +28918,441 @@
       <c r="BC177" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>q-fever</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>Q热</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N178" t="n">
+        <v>0</v>
+      </c>
+      <c r="O178" t="n">
+        <v>0</v>
+      </c>
+      <c r="R178" t="n">
+        <v>0</v>
+      </c>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO178" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP178" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR178" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS178" t="inlineStr"/>
+      <c r="AT178" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU178" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV178" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW178" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX178" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY178" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA178" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB178" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC178" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>q-fever</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>Q热</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N179" t="n">
+        <v>1</v>
+      </c>
+      <c r="O179" t="n">
+        <v>1</v>
+      </c>
+      <c r="R179" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
+      <c r="S179" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO179" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP179" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR179" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS179" t="inlineStr"/>
+      <c r="AT179" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU179" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV179" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW179" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX179" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY179" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA179" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB179" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC179" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>q-fever</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>Q热</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N180" t="n">
+        <v>0</v>
+      </c>
+      <c r="O180" t="n">
+        <v>0</v>
+      </c>
+      <c r="R180" t="n">
+        <v>0</v>
+      </c>
+      <c r="S180" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO180" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP180" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR180" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS180" t="inlineStr"/>
+      <c r="AT180" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU180" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV180" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW180" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX180" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY180" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA180" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB180" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC180" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -28954,7 +29389,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -29037,7 +29472,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="10">
@@ -29047,7 +29482,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="11">
@@ -29099,7 +29534,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>802</v>
+        <v>837</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d113/2026-2029.xlsx
+++ b/diseases/d113/2026-2029.xlsx
@@ -27715,13 +27715,13 @@
         </is>
       </c>
       <c r="N170" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O170" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="R170" t="n">
-        <v>0.1101843545855937</v>
+        <v>0.1138571664051135</v>
       </c>
       <c r="S170" t="inlineStr">
         <is>
@@ -29534,7 +29534,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>837</v>
+        <v>838</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d113/2026-2029.xlsx
+++ b/diseases/d113/2026-2029.xlsx
@@ -1989,7 +1989,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -5100,7 +5100,7 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN28" t="b">
@@ -8211,7 +8211,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -11319,7 +11319,7 @@
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN66" t="b">
@@ -14279,7 +14279,7 @@
       </c>
       <c r="AM84" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN84" t="b">
@@ -18390,7 +18390,7 @@
       </c>
       <c r="AM110" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN110" t="b">
@@ -22607,7 +22607,7 @@
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN137" t="b">
@@ -26005,7 +26005,7 @@
       </c>
       <c r="AM159" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN159" t="b">
@@ -28261,7 +28261,7 @@
       </c>
       <c r="AM173" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN173" t="b">

--- a/diseases/d113/2026-2029.xlsx
+++ b/diseases/d113/2026-2029.xlsx
@@ -35440,13 +35440,13 @@
         </is>
       </c>
       <c r="N224" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O224" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R224" t="n">
-        <v>0.005813909771376137</v>
+        <v>0.007751879695168184</v>
       </c>
       <c r="S224" t="inlineStr">
         <is>
@@ -37259,7 +37259,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1240</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d113/2026-2029.xlsx
+++ b/diseases/d113/2026-2029.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -921,6 +926,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1066,6 +1076,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1202,6 +1217,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1347,6 +1367,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1483,6 +1508,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1628,6 +1658,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1764,6 +1799,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1900,6 +1940,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2580,6 +2625,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2725,6 +2775,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3113,7 +3168,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -3679,6 +3734,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3975,6 +4035,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4271,6 +4336,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4567,6 +4637,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4863,6 +4938,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5011,6 +5091,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5156,6 +5241,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5301,6 +5391,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5446,6 +5541,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5591,6 +5691,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5727,6 +5832,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5872,6 +5982,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6008,6 +6123,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6144,6 +6264,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6824,6 +6949,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6969,6 +7099,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7357,7 +7492,7 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN44" t="b">
@@ -7923,6 +8058,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8219,6 +8359,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8515,6 +8660,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8811,6 +8961,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9107,6 +9262,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9255,6 +9415,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9400,6 +9565,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9545,6 +9715,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9690,6 +9865,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9835,6 +10015,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9980,6 +10165,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10125,6 +10315,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10270,6 +10465,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10415,6 +10615,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11095,6 +11300,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11240,6 +11450,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11628,7 +11843,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -12194,6 +12409,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12490,6 +12710,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12786,6 +13011,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13082,6 +13312,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13378,6 +13613,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13523,6 +13763,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO83" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13668,6 +13913,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13813,6 +14063,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13958,6 +14213,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO86" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14103,6 +14363,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO87" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14248,6 +14513,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14393,6 +14663,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14538,6 +14813,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14683,6 +14963,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15363,6 +15648,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO95" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15508,6 +15798,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15896,7 +16191,7 @@
       </c>
       <c r="AM98" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN98" t="b">
@@ -16610,6 +16905,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO102" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16906,6 +17206,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17202,6 +17507,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO106" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17498,6 +17808,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO108" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17643,6 +17958,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO109" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17788,6 +18108,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO110" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17933,6 +18258,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO111" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18078,6 +18408,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO112" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18223,6 +18558,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO113" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18368,6 +18708,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO114" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18504,6 +18849,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO115" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18649,6 +18999,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO116" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18785,6 +19140,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19465,6 +19825,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO121" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19610,6 +19975,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO122" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19998,7 +20368,7 @@
       </c>
       <c r="AM124" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN124" t="b">
@@ -20561,6 +20931,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO127" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20857,6 +21232,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO129" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21153,6 +21533,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO131" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21449,6 +21834,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO133" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21745,6 +22135,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO135" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22041,6 +22436,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO137" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22186,6 +22586,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO138" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22322,6 +22727,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO139" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22467,6 +22877,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO140" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22612,6 +23027,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO141" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22757,6 +23177,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO142" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22893,6 +23318,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO143" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23038,6 +23468,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO144" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23174,6 +23609,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO145" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23310,6 +23750,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO146" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23990,6 +24435,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO150" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24135,6 +24585,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO151" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24523,7 +24978,7 @@
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN153" t="b">
@@ -25086,6 +25541,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO156" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25376,6 +25836,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO158" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25666,6 +26131,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO160" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25956,6 +26426,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO162" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26246,6 +26721,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO164" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26391,6 +26871,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO165" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26536,6 +27021,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO166" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26681,6 +27171,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO167" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26826,6 +27321,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO168" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26971,6 +27471,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO169" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27116,6 +27621,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO170" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27261,6 +27771,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO171" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27406,6 +27921,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO172" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27551,6 +28071,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO173" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28073,13 +28598,13 @@
         </is>
       </c>
       <c r="N176" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O176" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R176" t="n">
-        <v>0.1110149228479591</v>
+        <v>0.122116415132755</v>
       </c>
       <c r="S176" t="inlineStr">
         <is>
@@ -28231,6 +28756,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO177" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28376,6 +28906,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO178" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28764,7 +29299,7 @@
       </c>
       <c r="AM180" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN180" t="b">
@@ -29472,6 +30007,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO184" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29762,6 +30302,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO186" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30052,6 +30597,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO188" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30342,6 +30892,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO190" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30632,6 +31187,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO192" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30777,6 +31337,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO193" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30922,6 +31487,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO194" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31058,6 +31628,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO195" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31203,6 +31778,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO196" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31339,6 +31919,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO197" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31484,6 +32069,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO198" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31629,6 +32219,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO199" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31765,6 +32360,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO200" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31858,12 +32458,12 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -31902,76 +32502,87 @@
       <c r="O201" t="n">
         <v>0</v>
       </c>
-      <c r="R201" t="n">
-        <v>0</v>
-      </c>
       <c r="S201" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_Q_FEVER_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO201" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP201" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR201" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS201" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ201" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS201" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_Q_FEVER_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT201" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU201" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV201" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ201" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA201" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB201" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC201" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -31998,17 +32609,17 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -32042,81 +32653,170 @@
         </is>
       </c>
       <c r="N202" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O202" t="n">
-        <v>10</v>
-      </c>
-      <c r="R202" t="n">
-        <v>0.01937969923792046</v>
-      </c>
-      <c r="S202" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="U202" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_Q_FEVER_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V202" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_Q_FEVER_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W202" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X202" t="inlineStr">
+        <is>
+          <t>Q Fever</t>
+        </is>
+      </c>
+      <c r="Y202" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z202" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB202" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC202" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD202" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE202" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF202" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG202" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH202" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI202" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ202" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK202" t="inlineStr">
+        <is>
+          <t>PHO IDTO current-year monthly preliminary q fever notifications; confirmed cases only under the July 2026 technical notes.</t>
+        </is>
+      </c>
+      <c r="AM202" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN202" t="b">
+        <v>1</v>
       </c>
       <c r="AO202" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP202" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR202" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS202" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ202" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS202" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_Q_FEVER_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT202" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU202" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV202" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ202" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA202" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB202" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC202" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -32148,12 +32848,12 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -32187,100 +32887,81 @@
         </is>
       </c>
       <c r="N203" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O203" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="R203" t="n">
-        <v>0</v>
+        <v>0.122116415132755</v>
       </c>
       <c r="S203" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U203" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_511_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA203" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO203" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP203" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ203" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR203" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS203" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_511_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS203" t="inlineStr"/>
       <c r="AT203" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU203" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV203" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>rest_api</t>
         </is>
       </c>
       <c r="AZ203" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="BA203" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="BB203" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="BC203" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>rest_api</t>
         </is>
       </c>
     </row>
@@ -32307,17 +32988,17 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -32356,34 +33037,12 @@
       <c r="O204" t="n">
         <v>0</v>
       </c>
-      <c r="U204" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_511_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V204" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_511_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W204" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X204" t="inlineStr">
-        <is>
-          <t>Q-feber</t>
-        </is>
-      </c>
-      <c r="Y204" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z204" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+      <c r="R204" t="n">
+        <v>0</v>
+      </c>
+      <c r="S204" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
@@ -32391,135 +33050,68 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB204" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC204" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD204" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE204" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF204" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG204" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH204" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI204" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ204" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK204" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM204" t="inlineStr">
-        <is>
-          <t>raw; revised</t>
-        </is>
-      </c>
-      <c r="AN204" t="b">
-        <v>1</v>
-      </c>
       <c r="AO204" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP204" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ204" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR204" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS204" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_511_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS204" t="inlineStr"/>
       <c r="AT204" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU204" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV204" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA204" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB204" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC204" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -32551,12 +33143,12 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -32590,24 +33182,19 @@
         </is>
       </c>
       <c r="N205" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O205" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R205" t="n">
-        <v>0</v>
+        <v>0.01937969923792046</v>
       </c>
       <c r="S205" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U205" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
-        </is>
-      </c>
       <c r="AA205" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -32615,75 +33202,66 @@
       </c>
       <c r="AO205" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP205" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ205" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR205" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS205" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS205" t="inlineStr"/>
       <c r="AT205" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU205" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV205" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ205" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA205" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB205" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC205" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -32710,17 +33288,17 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -32759,34 +33337,17 @@
       <c r="O206" t="n">
         <v>0</v>
       </c>
+      <c r="R206" t="n">
+        <v>0</v>
+      </c>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U206" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
-        </is>
-      </c>
-      <c r="V206" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
-        </is>
-      </c>
-      <c r="W206" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X206" t="inlineStr">
-        <is>
-          <t>Q-feber</t>
-        </is>
-      </c>
-      <c r="Y206" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z206" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>SER_NO_FHI_511_MONTHLY</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
@@ -32794,64 +33355,6 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB206" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC206" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD206" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE206" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF206" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG206" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH206" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI206" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ206" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK206" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
-        </is>
-      </c>
-      <c r="AM206" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN206" t="b">
-        <v>1</v>
-      </c>
       <c r="AO206" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -32874,7 +33377,7 @@
       </c>
       <c r="AS206" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
+          <t>SER_NO_FHI_511_MONTHLY</t>
         </is>
       </c>
       <c r="AT206" t="n">
@@ -32887,42 +33390,42 @@
       </c>
       <c r="AV206" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA206" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB206" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC206" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -32949,17 +33452,17 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -32993,81 +33496,175 @@
         </is>
       </c>
       <c r="N207" t="n">
+        <v>0</v>
+      </c>
+      <c r="O207" t="n">
+        <v>0</v>
+      </c>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_511_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V207" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_511_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W207" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X207" t="inlineStr">
+        <is>
+          <t>Q-feber</t>
+        </is>
+      </c>
+      <c r="Y207" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z207" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB207" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC207" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD207" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE207" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF207" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG207" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH207" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI207" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ207" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK207" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM207" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN207" t="b">
         <v>1</v>
       </c>
-      <c r="O207" t="n">
-        <v>1</v>
-      </c>
-      <c r="R207" t="n">
-        <v>0.0002865038132769385</v>
-      </c>
-      <c r="S207" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AO207" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP207" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ207" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR207" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS207" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS207" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_511_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT207" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU207" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV207" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA207" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB207" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC207" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -33099,12 +33696,12 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -33129,7 +33726,7 @@
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M208" t="inlineStr">
@@ -33151,68 +33748,87 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U208" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
+        </is>
+      </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO208" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP208" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ208" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR208" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS208" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS208" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
+        </is>
+      </c>
       <c r="AT208" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU208" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV208" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ208" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA208" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB208" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC208" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -33239,17 +33855,17 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -33274,7 +33890,7 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
@@ -33288,76 +33904,170 @@
       <c r="O209" t="n">
         <v>0</v>
       </c>
-      <c r="R209" t="n">
-        <v>0</v>
-      </c>
-      <c r="S209" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
+        </is>
+      </c>
+      <c r="V209" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
+        </is>
+      </c>
+      <c r="W209" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X209" t="inlineStr">
+        <is>
+          <t>Q-feber</t>
+        </is>
+      </c>
+      <c r="Y209" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z209" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA209" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB209" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC209" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD209" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE209" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF209" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG209" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH209" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI209" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ209" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK209" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM209" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN209" t="b">
+        <v>1</v>
       </c>
       <c r="AO209" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP209" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ209" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR209" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS209" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS209" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
+        </is>
+      </c>
       <c r="AT209" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU209" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV209" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ209" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA209" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB209" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC209" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -33419,7 +34129,7 @@
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
@@ -33439,6 +34149,11 @@
       <c r="S210" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO210" t="inlineStr">
@@ -33564,7 +34279,7 @@
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M211" t="inlineStr">
@@ -33709,7 +34424,7 @@
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M212" t="inlineStr">
@@ -33854,7 +34569,7 @@
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M213" t="inlineStr">
@@ -33874,6 +34589,11 @@
       <c r="S213" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO213" t="inlineStr">
@@ -33999,7 +34719,7 @@
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M214" t="inlineStr">
@@ -34114,12 +34834,12 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -34144,22 +34864,22 @@
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N215" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="O215" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="R215" t="n">
-        <v>0.1248756018636729</v>
+        <v>0</v>
       </c>
       <c r="S215" t="inlineStr">
         <is>
@@ -34192,42 +34912,42 @@
       </c>
       <c r="AV215" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW215" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX215" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY215" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ215" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA215" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB215" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC215" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -34259,12 +34979,12 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -34289,26 +35009,31 @@
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N216" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O216" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R216" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S216" t="inlineStr">
         <is>
-          <t>abs_computed</t>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO216" t="inlineStr">
@@ -34337,42 +35062,42 @@
       </c>
       <c r="AV216" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW216" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX216" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY216" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ216" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA216" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB216" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC216" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -34404,12 +35129,12 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -34434,26 +35159,26 @@
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N217" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O217" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="R217" t="n">
-        <v>0.138406628293429</v>
+        <v>0</v>
       </c>
       <c r="S217" t="inlineStr">
         <is>
-          <t>abs_computed</t>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AO217" t="inlineStr">
@@ -34482,42 +35207,42 @@
       </c>
       <c r="AV217" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW217" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX217" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY217" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ217" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA217" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB217" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC217" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -34549,12 +35274,12 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -34588,17 +35313,22 @@
         </is>
       </c>
       <c r="N218" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="O218" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="R218" t="n">
-        <v>0</v>
+        <v>0.1322212255027125</v>
       </c>
       <c r="S218" t="inlineStr">
         <is>
-          <t>abs_computed</t>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO218" t="inlineStr">
@@ -34632,12 +35362,12 @@
       </c>
       <c r="AW218" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr">
@@ -34652,12 +35382,12 @@
       </c>
       <c r="BA218" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB218" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC218" t="inlineStr">
@@ -34694,12 +35424,12 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -34733,17 +35463,22 @@
         </is>
       </c>
       <c r="N219" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O219" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="R219" t="n">
-        <v>0.2787718219533158</v>
+        <v>0</v>
       </c>
       <c r="S219" t="inlineStr">
         <is>
           <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA219" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO219" t="inlineStr">
@@ -34777,7 +35512,7 @@
       </c>
       <c r="AW219" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX219" t="inlineStr">
@@ -34797,7 +35532,7 @@
       </c>
       <c r="BA219" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB219" t="inlineStr">
@@ -34839,12 +35574,12 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -34878,17 +35613,22 @@
         </is>
       </c>
       <c r="N220" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O220" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R220" t="n">
-        <v>0</v>
+        <v>0.138406628293429</v>
       </c>
       <c r="S220" t="inlineStr">
         <is>
           <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO220" t="inlineStr">
@@ -34922,7 +35662,7 @@
       </c>
       <c r="AW220" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX220" t="inlineStr">
@@ -34942,7 +35682,7 @@
       </c>
       <c r="BA220" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB220" t="inlineStr">
@@ -34984,12 +35724,12 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -35022,9 +35762,23 @@
           <t>2026-09</t>
         </is>
       </c>
+      <c r="N221" t="n">
+        <v>0</v>
+      </c>
+      <c r="O221" t="n">
+        <v>0</v>
+      </c>
+      <c r="R221" t="n">
+        <v>0</v>
+      </c>
       <c r="S221" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO221" t="inlineStr">
@@ -35058,7 +35812,7 @@
       </c>
       <c r="AW221" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX221" t="inlineStr">
@@ -35078,7 +35832,7 @@
       </c>
       <c r="BA221" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB221" t="inlineStr">
@@ -35120,12 +35874,12 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -35158,9 +35912,23 @@
           <t>2026-09</t>
         </is>
       </c>
+      <c r="N222" t="n">
+        <v>16</v>
+      </c>
+      <c r="O222" t="n">
+        <v>16</v>
+      </c>
+      <c r="R222" t="n">
+        <v>0.2787718219533158</v>
+      </c>
       <c r="S222" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA222" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO222" t="inlineStr">
@@ -35194,7 +35962,7 @@
       </c>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
@@ -35214,7 +35982,7 @@
       </c>
       <c r="BA222" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB222" t="inlineStr">
@@ -35256,12 +36024,12 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -35306,6 +36074,11 @@
       <c r="S223" t="inlineStr">
         <is>
           <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO223" t="inlineStr">
@@ -35339,7 +36112,7 @@
       </c>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
@@ -35359,7 +36132,7 @@
       </c>
       <c r="BA223" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB223" t="inlineStr">
@@ -35401,12 +36174,12 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -35439,18 +36212,14 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N224" t="n">
-        <v>4</v>
-      </c>
-      <c r="O224" t="n">
-        <v>4</v>
-      </c>
-      <c r="R224" t="n">
-        <v>0.007751879695168184</v>
-      </c>
       <c r="S224" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA224" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO224" t="inlineStr">
@@ -35479,42 +36248,42 @@
       </c>
       <c r="AV224" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ224" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA224" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB224" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC224" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -35546,12 +36315,12 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -35584,23 +36353,9 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N225" t="n">
-        <v>0</v>
-      </c>
-      <c r="O225" t="n">
-        <v>0</v>
-      </c>
-      <c r="R225" t="n">
-        <v>0</v>
-      </c>
       <c r="S225" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U225" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_511_MONTHLY</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
@@ -35610,75 +36365,66 @@
       </c>
       <c r="AO225" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP225" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ225" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR225" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS225" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_511_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS225" t="inlineStr"/>
       <c r="AT225" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU225" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV225" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ225" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA225" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB225" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC225" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -35705,17 +36451,17 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -35754,34 +36500,12 @@
       <c r="O226" t="n">
         <v>0</v>
       </c>
-      <c r="U226" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_511_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V226" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_511_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W226" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X226" t="inlineStr">
-        <is>
-          <t>Q-feber</t>
-        </is>
-      </c>
-      <c r="Y226" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z226" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+      <c r="R226" t="n">
+        <v>0</v>
+      </c>
+      <c r="S226" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
@@ -35789,135 +36513,68 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB226" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC226" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD226" t="inlineStr">
+      <c r="AO226" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP226" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR226" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS226" t="inlineStr"/>
+      <c r="AT226" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU226" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV226" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE226" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF226" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG226" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH226" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI226" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ226" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK226" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM226" t="inlineStr">
-        <is>
-          <t>raw; revised</t>
-        </is>
-      </c>
-      <c r="AN226" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO226" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP226" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ226" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR226" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS226" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_511_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT226" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU226" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
-        </is>
-      </c>
-      <c r="AV226" t="inlineStr">
-        <is>
-          <t>fhi_msis</t>
-        </is>
-      </c>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ226" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA226" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB226" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC226" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -35949,12 +36606,12 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -35979,7 +36636,7 @@
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M227" t="inlineStr">
@@ -35994,11 +36651,16 @@
         <v>4</v>
       </c>
       <c r="R227" t="n">
-        <v>0.001146015253107754</v>
+        <v>0.007751879695168184</v>
       </c>
       <c r="S227" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA227" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO227" t="inlineStr">
@@ -36027,42 +36689,42 @@
       </c>
       <c r="AV227" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ227" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA227" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB227" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC227" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -36094,12 +36756,12 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -36124,7 +36786,7 @@
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M228" t="inlineStr">
@@ -36146,68 +36808,87 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U228" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_511_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA228" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO228" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP228" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ228" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR228" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS228" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS228" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_511_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT228" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU228" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV228" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ228" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA228" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB228" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC228" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -36234,17 +36915,17 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -36269,7 +36950,7 @@
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M229" t="inlineStr">
@@ -36283,76 +36964,170 @@
       <c r="O229" t="n">
         <v>0</v>
       </c>
-      <c r="R229" t="n">
-        <v>0</v>
-      </c>
-      <c r="S229" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U229" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_511_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V229" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_511_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W229" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X229" t="inlineStr">
+        <is>
+          <t>Q-feber</t>
+        </is>
+      </c>
+      <c r="Y229" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z229" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA229" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB229" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC229" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD229" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE229" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF229" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG229" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH229" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI229" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ229" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK229" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM229" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN229" t="b">
+        <v>1</v>
       </c>
       <c r="AO229" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP229" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ229" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR229" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS229" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS229" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_511_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT229" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU229" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV229" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW229" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ229" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA229" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB229" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC229" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -36384,12 +37159,12 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -36414,7 +37189,7 @@
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M230" t="inlineStr">
@@ -36423,81 +37198,100 @@
         </is>
       </c>
       <c r="N230" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O230" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R230" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0</v>
       </c>
       <c r="S230" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U230" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
+        </is>
+      </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO230" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP230" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ230" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR230" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS230" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS230" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
+        </is>
+      </c>
       <c r="AT230" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU230" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV230" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ230" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA230" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB230" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC230" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -36524,17 +37318,17 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -36559,7 +37353,7 @@
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M231" t="inlineStr">
@@ -36573,76 +37367,170 @@
       <c r="O231" t="n">
         <v>0</v>
       </c>
-      <c r="R231" t="n">
-        <v>0</v>
-      </c>
-      <c r="S231" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U231" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
+        </is>
+      </c>
+      <c r="V231" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
+        </is>
+      </c>
+      <c r="W231" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X231" t="inlineStr">
+        <is>
+          <t>Q-feber</t>
+        </is>
+      </c>
+      <c r="Y231" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z231" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA231" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB231" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC231" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD231" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE231" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF231" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG231" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH231" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI231" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ231" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK231" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM231" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN231" t="b">
+        <v>1</v>
       </c>
       <c r="AO231" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP231" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ231" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR231" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS231" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS231" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
+        </is>
+      </c>
       <c r="AT231" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU231" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV231" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ231" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA231" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB231" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC231" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -36704,7 +37592,7 @@
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="M232" t="inlineStr">
@@ -36713,17 +37601,22 @@
         </is>
       </c>
       <c r="N232" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O232" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R232" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0.001146015253107754</v>
       </c>
       <c r="S232" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO232" t="inlineStr">
@@ -36849,7 +37742,7 @@
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="M233" t="inlineStr">
@@ -36964,12 +37857,12 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -36994,12 +37887,12 @@
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N234" t="n">
@@ -37042,42 +37935,1335 @@
       </c>
       <c r="AV234" t="inlineStr">
         <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW234" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX234" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY234" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA234" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB234" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC234" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>q-fever</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>Q热</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N235" t="n">
+        <v>1</v>
+      </c>
+      <c r="O235" t="n">
+        <v>1</v>
+      </c>
+      <c r="R235" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
+      <c r="S235" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA235" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO235" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP235" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR235" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS235" t="inlineStr"/>
+      <c r="AT235" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU235" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV235" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW235" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX235" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY235" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA235" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB235" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC235" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>q-fever</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>Q热</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N236" t="n">
+        <v>0</v>
+      </c>
+      <c r="O236" t="n">
+        <v>0</v>
+      </c>
+      <c r="R236" t="n">
+        <v>0</v>
+      </c>
+      <c r="S236" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO236" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP236" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR236" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS236" t="inlineStr"/>
+      <c r="AT236" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU236" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV236" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW236" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX236" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY236" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA236" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB236" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC236" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>q-fever</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>Q热</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N237" t="n">
+        <v>1</v>
+      </c>
+      <c r="O237" t="n">
+        <v>1</v>
+      </c>
+      <c r="R237" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
+      <c r="S237" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA237" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO237" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP237" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR237" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS237" t="inlineStr"/>
+      <c r="AT237" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU237" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV237" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW237" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX237" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY237" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA237" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB237" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC237" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>q-fever</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>Q热</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N238" t="n">
+        <v>0</v>
+      </c>
+      <c r="O238" t="n">
+        <v>0</v>
+      </c>
+      <c r="R238" t="n">
+        <v>0</v>
+      </c>
+      <c r="S238" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO238" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP238" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR238" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS238" t="inlineStr"/>
+      <c r="AT238" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU238" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV238" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW238" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX238" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY238" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ238" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA238" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB238" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC238" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>q-fever</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>Q热</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N239" t="n">
+        <v>0</v>
+      </c>
+      <c r="O239" t="n">
+        <v>0</v>
+      </c>
+      <c r="R239" t="n">
+        <v>0</v>
+      </c>
+      <c r="S239" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA239" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO239" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP239" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR239" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS239" t="inlineStr"/>
+      <c r="AT239" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU239" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV239" t="inlineStr">
+        <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW234" t="inlineStr">
+      <c r="AW239" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX234" t="inlineStr">
+      <c r="AX239" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY234" t="inlineStr">
+      <c r="AY239" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ234" t="inlineStr">
+      <c r="AZ239" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA234" t="inlineStr">
+      <c r="BA239" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB234" t="inlineStr">
+      <c r="BB239" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC234" t="inlineStr">
+      <c r="BC239" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>q-fever</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>Q热</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N240" t="n">
+        <v>0</v>
+      </c>
+      <c r="O240" t="n">
+        <v>0</v>
+      </c>
+      <c r="R240" t="n">
+        <v>0</v>
+      </c>
+      <c r="S240" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U240" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_511_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA240" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO240" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP240" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ240" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR240" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS240" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_511_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT240" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU240" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV240" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW240" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX240" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY240" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ240" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA240" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB240" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC240" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>q-fever</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>Q热</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N241" t="n">
+        <v>0</v>
+      </c>
+      <c r="O241" t="n">
+        <v>0</v>
+      </c>
+      <c r="U241" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_511_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V241" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_511_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W241" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X241" t="inlineStr">
+        <is>
+          <t>Q-feber</t>
+        </is>
+      </c>
+      <c r="Y241" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z241" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA241" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB241" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC241" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD241" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE241" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF241" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG241" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH241" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI241" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ241" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK241" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM241" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN241" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO241" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP241" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ241" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR241" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS241" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_511_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT241" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU241" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV241" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW241" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX241" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY241" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ241" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA241" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB241" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC241" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>q-fever</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>Q热</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N242" t="n">
+        <v>1</v>
+      </c>
+      <c r="O242" t="n">
+        <v>1</v>
+      </c>
+      <c r="R242" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
+      <c r="S242" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA242" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO242" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP242" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR242" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS242" t="inlineStr"/>
+      <c r="AT242" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU242" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV242" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW242" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX242" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY242" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ242" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA242" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB242" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC242" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -37114,7 +39300,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -37197,7 +39383,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>209</v>
+        <v>214</v>
       </c>
     </row>
     <row r="10">
@@ -37207,7 +39393,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>233</v>
+        <v>241</v>
       </c>
     </row>
     <row r="11">
@@ -37227,7 +39413,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13">
@@ -37259,7 +39445,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1241</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d113/2026-2029.xlsx
+++ b/diseases/d113/2026-2029.xlsx
@@ -36645,13 +36645,13 @@
         </is>
       </c>
       <c r="N227" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O227" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R227" t="n">
-        <v>0.007751879695168184</v>
+        <v>0.009689849618960231</v>
       </c>
       <c r="S227" t="inlineStr">
         <is>
@@ -39445,7 +39445,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1256</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d113/2026-2029.xlsx
+++ b/diseases/d113/2026-2029.xlsx
@@ -35313,13 +35313,13 @@
         </is>
       </c>
       <c r="N218" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="O218" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="R218" t="n">
-        <v>0.1322212255027125</v>
+        <v>0.1432396609612718</v>
       </c>
       <c r="S218" t="inlineStr">
         <is>
@@ -39264,6 +39264,151 @@
       <c r="BC242" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>q-fever</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>Q热</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N243" t="n">
+        <v>0</v>
+      </c>
+      <c r="O243" t="n">
+        <v>0</v>
+      </c>
+      <c r="R243" t="n">
+        <v>0</v>
+      </c>
+      <c r="S243" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO243" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP243" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR243" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS243" t="inlineStr"/>
+      <c r="AT243" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU243" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV243" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW243" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX243" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY243" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ243" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA243" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB243" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC243" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -39300,7 +39445,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -39383,7 +39528,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="10">
@@ -39393,7 +39538,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="11">
@@ -39445,7 +39590,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1257</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d113/2026-2029.xlsx
+++ b/diseases/d113/2026-2029.xlsx
@@ -4024,9 +4024,6 @@
       <c r="O22" t="n">
         <v>1</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -4325,9 +4322,6 @@
       <c r="O24" t="n">
         <v>1</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -4626,9 +4620,6 @@
       <c r="O26" t="n">
         <v>1</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -8348,9 +8339,6 @@
       <c r="O49" t="n">
         <v>4</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0.001146015253107754</v>
       </c>
@@ -8649,9 +8637,6 @@
       <c r="O51" t="n">
         <v>1</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -12699,9 +12684,6 @@
       <c r="O76" t="n">
         <v>1</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -16894,9 +16876,6 @@
       <c r="O102" t="n">
         <v>1</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -17797,9 +17776,6 @@
       <c r="O108" t="n">
         <v>3</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0.0008595114398308156</v>
       </c>
@@ -21221,9 +21197,6 @@
       <c r="O129" t="n">
         <v>1</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="R129" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -21522,9 +21495,6 @@
       <c r="O131" t="n">
         <v>1</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -21823,9 +21793,6 @@
       <c r="O133" t="n">
         <v>2</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>0.0005730076265538771</v>
       </c>
@@ -22124,9 +22091,6 @@
       <c r="O135" t="n">
         <v>1</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -39409,6 +39373,156 @@
       <c r="BC243" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>q-fever</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>Q热</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N244" t="n">
+        <v>1</v>
+      </c>
+      <c r="O244" t="n">
+        <v>1</v>
+      </c>
+      <c r="R244" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
+      <c r="S244" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA244" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO244" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP244" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR244" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS244" t="inlineStr"/>
+      <c r="AT244" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU244" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV244" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW244" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX244" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY244" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ244" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA244" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB244" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC244" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -39445,7 +39559,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -39528,7 +39642,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="10">
@@ -39538,7 +39652,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="11">
@@ -39590,7 +39704,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1260</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="16">
